--- a/artfynd/A 59107-2025 artfynd.xlsx
+++ b/artfynd/A 59107-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,6 +891,3710 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130058003</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80193</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>575401</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6970182</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130058013</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80228</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>575046</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6970437</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130057976</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>575355</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6970253</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130057987</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>575159</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6970484</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130057990</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>575209</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6970519</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130057992</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>575633</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6970534</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130058010</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79088</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>575292</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6970422</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130057981</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>575188</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6970404</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130057977</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>575326</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6970235</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130058007</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80193</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>575156</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6970589</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130057979</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>575310</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6970285</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130057980</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>575240</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6970340</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130058000</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80222</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>575245</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6970511</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130057982</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>575171</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6970392</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130057986</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>574906</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6970504</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130057998</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>575378</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6970293</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130057984</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>574929</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6970479</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130058004</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80193</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>575255</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6970243</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130057985</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>574905</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6970496</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130057975</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>575392</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6970254</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130057996</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>575595</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6970425</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1 ex, födosökande</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130057991</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>575309</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6970453</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130058014</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80228</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>575230</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6970505</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130058006</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80193</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>575224</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6970509</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130057974</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>575394</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6970263</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130058001</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80194</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>575248</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6970510</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130058005</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80193</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>575268</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6970343</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130058008</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80229</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>575396</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6970178</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130058002</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80097</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>575187</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6970552</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130057988</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>575150</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6970497</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130057999</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>575387</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6970271</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130057989</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>575153</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6970582</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130058011</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79088</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>575417</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6970259</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130057983</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>575080</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6970402</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>130058012</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80228</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>575222</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6970329</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130057997</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>575343</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6970427</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>130057978</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Långmarkflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>575331</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6970309</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59107-2025 artfynd.xlsx
+++ b/artfynd/A 59107-2025 artfynd.xlsx
@@ -1694,10 +1694,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130057977</v>
+        <v>130058007</v>
       </c>
       <c r="B12" t="n">
-        <v>57740</v>
+        <v>80193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,21 +1705,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575326</v>
+        <v>575156</v>
       </c>
       <c r="R12" t="n">
-        <v>6970235</v>
+        <v>6970589</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,11 +1765,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1796,10 +1791,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130058007</v>
+        <v>130057977</v>
       </c>
       <c r="B13" t="n">
-        <v>80193</v>
+        <v>57740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1807,21 +1802,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1831,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575156</v>
+        <v>575326</v>
       </c>
       <c r="R13" t="n">
-        <v>6970589</v>
+        <v>6970235</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,6 +1862,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2903,7 +2903,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130057996</v>
+        <v>130057991</v>
       </c>
       <c r="B24" t="n">
         <v>57740</v>
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575595</v>
+        <v>575309</v>
       </c>
       <c r="R24" t="n">
-        <v>6970425</v>
+        <v>6970453</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>1 ex, födosökande</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3005,32 +3005,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130057991</v>
+        <v>130058014</v>
       </c>
       <c r="B25" t="n">
-        <v>57740</v>
+        <v>80228</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575309</v>
+        <v>575230</v>
       </c>
       <c r="R25" t="n">
-        <v>6970453</v>
+        <v>6970505</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3076,11 +3076,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3107,32 +3102,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130058014</v>
+        <v>130058006</v>
       </c>
       <c r="B26" t="n">
-        <v>80228</v>
+        <v>80193</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3142,10 +3137,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575230</v>
+        <v>575224</v>
       </c>
       <c r="R26" t="n">
-        <v>6970505</v>
+        <v>6970509</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3204,10 +3199,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130058006</v>
+        <v>130057974</v>
       </c>
       <c r="B27" t="n">
-        <v>80193</v>
+        <v>57740</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3215,21 +3210,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3239,10 +3234,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575224</v>
+        <v>575394</v>
       </c>
       <c r="R27" t="n">
-        <v>6970509</v>
+        <v>6970263</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3275,6 +3270,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3301,10 +3301,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130057974</v>
+        <v>130058001</v>
       </c>
       <c r="B28" t="n">
-        <v>57740</v>
+        <v>80194</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3312,21 +3312,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575394</v>
+        <v>575248</v>
       </c>
       <c r="R28" t="n">
-        <v>6970263</v>
+        <v>6970510</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3372,11 +3372,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3403,10 +3398,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130058001</v>
+        <v>130058005</v>
       </c>
       <c r="B29" t="n">
-        <v>80194</v>
+        <v>80193</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3414,21 +3409,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3438,10 +3433,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575248</v>
+        <v>575268</v>
       </c>
       <c r="R29" t="n">
-        <v>6970510</v>
+        <v>6970343</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3500,32 +3495,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130058005</v>
+        <v>130058008</v>
       </c>
       <c r="B30" t="n">
-        <v>80193</v>
+        <v>80229</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3535,10 +3530,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575268</v>
+        <v>575396</v>
       </c>
       <c r="R30" t="n">
-        <v>6970343</v>
+        <v>6970178</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3597,10 +3592,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130058008</v>
+        <v>130058002</v>
       </c>
       <c r="B31" t="n">
-        <v>80229</v>
+        <v>80097</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3608,21 +3603,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3632,10 +3627,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575396</v>
+        <v>575187</v>
       </c>
       <c r="R31" t="n">
-        <v>6970178</v>
+        <v>6970552</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3694,32 +3689,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130058002</v>
+        <v>130057988</v>
       </c>
       <c r="B32" t="n">
-        <v>80097</v>
+        <v>57740</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3729,10 +3724,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>575187</v>
+        <v>575150</v>
       </c>
       <c r="R32" t="n">
-        <v>6970552</v>
+        <v>6970497</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3765,6 +3760,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3791,7 +3791,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130057988</v>
+        <v>130057999</v>
       </c>
       <c r="B33" t="n">
         <v>57740</v>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>575150</v>
+        <v>575387</v>
       </c>
       <c r="R33" t="n">
-        <v>6970497</v>
+        <v>6970271</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3893,7 +3893,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130057999</v>
+        <v>130057989</v>
       </c>
       <c r="B34" t="n">
         <v>57740</v>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575387</v>
+        <v>575153</v>
       </c>
       <c r="R34" t="n">
-        <v>6970271</v>
+        <v>6970582</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3995,10 +3995,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130057989</v>
+        <v>130058011</v>
       </c>
       <c r="B35" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4006,21 +4006,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575153</v>
+        <v>575417</v>
       </c>
       <c r="R35" t="n">
-        <v>6970582</v>
+        <v>6970259</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4066,11 +4066,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4097,10 +4092,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130058011</v>
+        <v>130057983</v>
       </c>
       <c r="B36" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4108,21 +4103,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4132,10 +4127,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575417</v>
+        <v>575080</v>
       </c>
       <c r="R36" t="n">
-        <v>6970259</v>
+        <v>6970402</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4168,6 +4163,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4194,32 +4194,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130057983</v>
+        <v>130058012</v>
       </c>
       <c r="B37" t="n">
-        <v>57740</v>
+        <v>80228</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4229,10 +4229,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575080</v>
+        <v>575222</v>
       </c>
       <c r="R37" t="n">
-        <v>6970402</v>
+        <v>6970329</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4265,11 +4265,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4296,32 +4291,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130058012</v>
+        <v>130057997</v>
       </c>
       <c r="B38" t="n">
-        <v>80228</v>
+        <v>57740</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4331,10 +4326,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575222</v>
+        <v>575343</v>
       </c>
       <c r="R38" t="n">
-        <v>6970329</v>
+        <v>6970427</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4367,6 +4362,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4393,7 +4393,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130057997</v>
+        <v>130057978</v>
       </c>
       <c r="B39" t="n">
         <v>57740</v>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>575343</v>
+        <v>575331</v>
       </c>
       <c r="R39" t="n">
-        <v>6970427</v>
+        <v>6970309</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4495,7 +4495,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130057978</v>
+        <v>130057996</v>
       </c>
       <c r="B40" t="n">
         <v>57740</v>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>575331</v>
+        <v>575595</v>
       </c>
       <c r="R40" t="n">
-        <v>6970309</v>
+        <v>6970425</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>1 ex, födosökande</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 59107-2025 artfynd.xlsx
+++ b/artfynd/A 59107-2025 artfynd.xlsx
@@ -1694,10 +1694,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130058007</v>
+        <v>130057977</v>
       </c>
       <c r="B12" t="n">
-        <v>80193</v>
+        <v>57740</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,21 +1705,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575156</v>
+        <v>575326</v>
       </c>
       <c r="R12" t="n">
-        <v>6970589</v>
+        <v>6970235</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,6 +1765,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1791,10 +1796,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130057977</v>
+        <v>130058007</v>
       </c>
       <c r="B13" t="n">
-        <v>57740</v>
+        <v>80193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1802,21 +1807,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1831,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575326</v>
+        <v>575156</v>
       </c>
       <c r="R13" t="n">
-        <v>6970235</v>
+        <v>6970589</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,11 +1867,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 59107-2025 artfynd.xlsx
+++ b/artfynd/A 59107-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>130058003</v>
       </c>
       <c r="B4" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>130058013</v>
       </c>
       <c r="B5" t="n">
-        <v>80228</v>
+        <v>80229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>130058010</v>
       </c>
       <c r="B10" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,10 +1694,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130057977</v>
+        <v>130058007</v>
       </c>
       <c r="B12" t="n">
-        <v>57740</v>
+        <v>80194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,21 +1705,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575326</v>
+        <v>575156</v>
       </c>
       <c r="R12" t="n">
-        <v>6970235</v>
+        <v>6970589</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,11 +1765,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1796,10 +1791,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130058007</v>
+        <v>130057977</v>
       </c>
       <c r="B13" t="n">
-        <v>80193</v>
+        <v>57740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1807,21 +1802,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1831,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575156</v>
+        <v>575326</v>
       </c>
       <c r="R13" t="n">
-        <v>6970589</v>
+        <v>6970235</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,6 +1862,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2100,7 +2100,7 @@
         <v>130058000</v>
       </c>
       <c r="B16" t="n">
-        <v>80222</v>
+        <v>80223</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>130058004</v>
       </c>
       <c r="B21" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>130058014</v>
       </c>
       <c r="B25" t="n">
-        <v>80228</v>
+        <v>80229</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>130058006</v>
       </c>
       <c r="B26" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3199,10 +3199,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130057974</v>
+        <v>130058001</v>
       </c>
       <c r="B27" t="n">
-        <v>57740</v>
+        <v>80195</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3210,21 +3210,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575394</v>
+        <v>575248</v>
       </c>
       <c r="R27" t="n">
-        <v>6970263</v>
+        <v>6970510</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3270,11 +3270,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3301,10 +3296,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130058001</v>
+        <v>130057974</v>
       </c>
       <c r="B28" t="n">
-        <v>80194</v>
+        <v>57740</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3312,21 +3307,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3336,10 +3331,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575248</v>
+        <v>575394</v>
       </c>
       <c r="R28" t="n">
-        <v>6970510</v>
+        <v>6970263</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3372,6 +3367,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3401,7 +3401,7 @@
         <v>130058005</v>
       </c>
       <c r="B29" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>130058008</v>
       </c>
       <c r="B30" t="n">
-        <v>80229</v>
+        <v>80230</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>130058002</v>
       </c>
       <c r="B31" t="n">
-        <v>80097</v>
+        <v>80098</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3791,10 +3791,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130057999</v>
+        <v>130058011</v>
       </c>
       <c r="B33" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3802,21 +3802,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>575387</v>
+        <v>575417</v>
       </c>
       <c r="R33" t="n">
-        <v>6970271</v>
+        <v>6970259</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3862,11 +3862,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3893,7 +3888,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130057989</v>
+        <v>130057999</v>
       </c>
       <c r="B34" t="n">
         <v>57740</v>
@@ -3928,10 +3923,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575153</v>
+        <v>575387</v>
       </c>
       <c r="R34" t="n">
-        <v>6970582</v>
+        <v>6970271</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3995,10 +3990,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130058011</v>
+        <v>130057989</v>
       </c>
       <c r="B35" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4006,21 +4001,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4030,10 +4025,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575417</v>
+        <v>575153</v>
       </c>
       <c r="R35" t="n">
-        <v>6970259</v>
+        <v>6970582</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4066,6 +4061,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4092,32 +4092,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130057983</v>
+        <v>130058012</v>
       </c>
       <c r="B36" t="n">
-        <v>57740</v>
+        <v>80229</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4127,10 +4127,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575080</v>
+        <v>575222</v>
       </c>
       <c r="R36" t="n">
-        <v>6970402</v>
+        <v>6970329</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4163,11 +4163,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4194,32 +4189,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130058012</v>
+        <v>130057983</v>
       </c>
       <c r="B37" t="n">
-        <v>80228</v>
+        <v>57740</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4229,10 +4224,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575222</v>
+        <v>575080</v>
       </c>
       <c r="R37" t="n">
-        <v>6970329</v>
+        <v>6970402</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4265,6 +4260,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 59107-2025 artfynd.xlsx
+++ b/artfynd/A 59107-2025 artfynd.xlsx
@@ -1694,10 +1694,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130057977</v>
+        <v>130058007</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,21 +1705,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575326</v>
+        <v>575156</v>
       </c>
       <c r="R12" t="n">
-        <v>6970235</v>
+        <v>6970589</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,11 +1765,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1796,10 +1791,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130058007</v>
+        <v>130057977</v>
       </c>
       <c r="B13" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1807,21 +1802,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1831,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575156</v>
+        <v>575326</v>
       </c>
       <c r="R13" t="n">
-        <v>6970589</v>
+        <v>6970235</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,6 +1862,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 59107-2025 artfynd.xlsx
+++ b/artfynd/A 59107-2025 artfynd.xlsx
@@ -1495,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130058010</v>
+        <v>130057981</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1506,21 +1506,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575292</v>
+        <v>575188</v>
       </c>
       <c r="R10" t="n">
-        <v>6970422</v>
+        <v>6970404</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,6 +1566,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1592,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130057981</v>
+        <v>130058010</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,21 +1608,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1627,10 +1632,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575188</v>
+        <v>575292</v>
       </c>
       <c r="R11" t="n">
-        <v>6970404</v>
+        <v>6970422</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,11 +1668,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1694,10 +1694,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130058007</v>
+        <v>130057977</v>
       </c>
       <c r="B12" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,21 +1705,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575156</v>
+        <v>575326</v>
       </c>
       <c r="R12" t="n">
-        <v>6970589</v>
+        <v>6970235</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,6 +1765,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1791,10 +1796,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130057977</v>
+        <v>130058007</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1802,21 +1807,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1826,10 +1831,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575326</v>
+        <v>575156</v>
       </c>
       <c r="R13" t="n">
-        <v>6970235</v>
+        <v>6970589</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,11 +1867,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3791,10 +3791,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130058011</v>
+        <v>130057999</v>
       </c>
       <c r="B33" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3802,21 +3802,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>575417</v>
+        <v>575387</v>
       </c>
       <c r="R33" t="n">
-        <v>6970259</v>
+        <v>6970271</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3862,6 +3862,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3888,7 +3893,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130057999</v>
+        <v>130057989</v>
       </c>
       <c r="B34" t="n">
         <v>57741</v>
@@ -3923,10 +3928,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575387</v>
+        <v>575153</v>
       </c>
       <c r="R34" t="n">
-        <v>6970271</v>
+        <v>6970582</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3990,10 +3995,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130057989</v>
+        <v>130058011</v>
       </c>
       <c r="B35" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4001,21 +4006,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4025,10 +4030,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575153</v>
+        <v>575417</v>
       </c>
       <c r="R35" t="n">
-        <v>6970582</v>
+        <v>6970259</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4061,11 +4066,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 59107-2025 artfynd.xlsx
+++ b/artfynd/A 59107-2025 artfynd.xlsx
@@ -1291,7 +1291,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130057990</v>
+        <v>130057992</v>
       </c>
       <c r="B8" t="n">
         <v>57741</v>
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575209</v>
+        <v>575633</v>
       </c>
       <c r="R8" t="n">
-        <v>6970519</v>
+        <v>6970534</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,7 +1393,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130057992</v>
+        <v>130057990</v>
       </c>
       <c r="B9" t="n">
         <v>57741</v>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575633</v>
+        <v>575209</v>
       </c>
       <c r="R9" t="n">
-        <v>6970534</v>
+        <v>6970519</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130057981</v>
+        <v>130058010</v>
       </c>
       <c r="B10" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1506,21 +1506,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575188</v>
+        <v>575292</v>
       </c>
       <c r="R10" t="n">
-        <v>6970404</v>
+        <v>6970422</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,11 +1566,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1597,10 +1592,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130058010</v>
+        <v>130057981</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,21 +1603,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1632,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575292</v>
+        <v>575188</v>
       </c>
       <c r="R11" t="n">
-        <v>6970422</v>
+        <v>6970404</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,6 +1663,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1694,10 +1694,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130057977</v>
+        <v>130058007</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1705,21 +1705,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575326</v>
+        <v>575156</v>
       </c>
       <c r="R12" t="n">
-        <v>6970235</v>
+        <v>6970589</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,11 +1765,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1796,10 +1791,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130058007</v>
+        <v>130057977</v>
       </c>
       <c r="B13" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1807,21 +1802,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1831,10 +1826,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575156</v>
+        <v>575326</v>
       </c>
       <c r="R13" t="n">
-        <v>6970589</v>
+        <v>6970235</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,6 +1862,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2602,10 +2602,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130058004</v>
+        <v>130057985</v>
       </c>
       <c r="B21" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2613,21 +2613,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575255</v>
+        <v>574905</v>
       </c>
       <c r="R21" t="n">
-        <v>6970243</v>
+        <v>6970496</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2673,6 +2673,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2699,7 +2704,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130057985</v>
+        <v>130057975</v>
       </c>
       <c r="B22" t="n">
         <v>57741</v>
@@ -2734,10 +2739,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574905</v>
+        <v>575392</v>
       </c>
       <c r="R22" t="n">
-        <v>6970496</v>
+        <v>6970254</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2801,10 +2806,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130057975</v>
+        <v>130058004</v>
       </c>
       <c r="B23" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,21 +2817,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2836,10 +2841,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575392</v>
+        <v>575255</v>
       </c>
       <c r="R23" t="n">
-        <v>6970254</v>
+        <v>6970243</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2872,11 +2877,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3199,10 +3199,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130057974</v>
+        <v>130058001</v>
       </c>
       <c r="B27" t="n">
-        <v>57741</v>
+        <v>80201</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3210,21 +3210,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575394</v>
+        <v>575248</v>
       </c>
       <c r="R27" t="n">
-        <v>6970263</v>
+        <v>6970510</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3270,11 +3270,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3301,10 +3296,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130058001</v>
+        <v>130057974</v>
       </c>
       <c r="B28" t="n">
-        <v>80201</v>
+        <v>57741</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3312,21 +3307,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3336,10 +3331,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575248</v>
+        <v>575394</v>
       </c>
       <c r="R28" t="n">
-        <v>6970510</v>
+        <v>6970263</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3372,6 +3367,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4291,7 +4291,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130057997</v>
+        <v>130057978</v>
       </c>
       <c r="B38" t="n">
         <v>57741</v>
@@ -4326,10 +4326,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575343</v>
+        <v>575331</v>
       </c>
       <c r="R38" t="n">
-        <v>6970427</v>
+        <v>6970309</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4393,7 +4393,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130057978</v>
+        <v>130057997</v>
       </c>
       <c r="B39" t="n">
         <v>57741</v>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>575331</v>
+        <v>575343</v>
       </c>
       <c r="R39" t="n">
-        <v>6970309</v>
+        <v>6970427</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 59107-2025 artfynd.xlsx
+++ b/artfynd/A 59107-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>130058003</v>
       </c>
       <c r="B4" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>130058013</v>
       </c>
       <c r="B5" t="n">
-        <v>80235</v>
+        <v>80320</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>130057976</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         <v>130057987</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130057992</v>
+        <v>130057990</v>
       </c>
       <c r="B8" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575633</v>
+        <v>575209</v>
       </c>
       <c r="R8" t="n">
-        <v>6970534</v>
+        <v>6970519</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130057990</v>
+        <v>130057992</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575209</v>
+        <v>575633</v>
       </c>
       <c r="R9" t="n">
-        <v>6970519</v>
+        <v>6970534</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,7 +1498,7 @@
         <v>130058010</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>130057981</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>130058007</v>
       </c>
       <c r="B12" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>130057977</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>130057979</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>130057980</v>
       </c>
       <c r="B15" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>130058000</v>
       </c>
       <c r="B16" t="n">
-        <v>80229</v>
+        <v>80314</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,10 +2194,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130057982</v>
+        <v>130057998</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2229,10 +2229,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575171</v>
+        <v>575378</v>
       </c>
       <c r="R17" t="n">
-        <v>6970392</v>
+        <v>6970293</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,10 +2296,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130057986</v>
+        <v>130057982</v>
       </c>
       <c r="B18" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574906</v>
+        <v>575171</v>
       </c>
       <c r="R18" t="n">
-        <v>6970504</v>
+        <v>6970392</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2398,10 +2398,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130057998</v>
+        <v>130057986</v>
       </c>
       <c r="B19" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575378</v>
+        <v>574906</v>
       </c>
       <c r="R19" t="n">
-        <v>6970293</v>
+        <v>6970504</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2503,7 +2503,7 @@
         <v>130057984</v>
       </c>
       <c r="B20" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>130057985</v>
       </c>
       <c r="B21" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>130057975</v>
       </c>
       <c r="B22" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>130058004</v>
       </c>
       <c r="B23" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>130057991</v>
       </c>
       <c r="B24" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>130058014</v>
       </c>
       <c r="B25" t="n">
-        <v>80235</v>
+        <v>80320</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>130058006</v>
       </c>
       <c r="B26" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3199,10 +3199,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130058001</v>
+        <v>130057974</v>
       </c>
       <c r="B27" t="n">
-        <v>80201</v>
+        <v>57826</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3210,21 +3210,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575248</v>
+        <v>575394</v>
       </c>
       <c r="R27" t="n">
-        <v>6970510</v>
+        <v>6970263</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3270,6 +3270,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3296,10 +3301,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130057974</v>
+        <v>130058001</v>
       </c>
       <c r="B28" t="n">
-        <v>57741</v>
+        <v>80286</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3307,21 +3312,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3331,10 +3336,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575394</v>
+        <v>575248</v>
       </c>
       <c r="R28" t="n">
-        <v>6970263</v>
+        <v>6970510</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3367,11 +3372,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3401,7 +3401,7 @@
         <v>130058005</v>
       </c>
       <c r="B29" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3495,10 +3495,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130058002</v>
+        <v>130058008</v>
       </c>
       <c r="B30" t="n">
-        <v>80104</v>
+        <v>80321</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3506,21 +3506,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6456</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3530,10 +3530,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575187</v>
+        <v>575396</v>
       </c>
       <c r="R30" t="n">
-        <v>6970552</v>
+        <v>6970178</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3592,10 +3592,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130058008</v>
+        <v>130058002</v>
       </c>
       <c r="B31" t="n">
-        <v>80236</v>
+        <v>80189</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3603,21 +3603,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>6456</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575396</v>
+        <v>575187</v>
       </c>
       <c r="R31" t="n">
-        <v>6970178</v>
+        <v>6970552</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3692,7 +3692,7 @@
         <v>130057988</v>
       </c>
       <c r="B32" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>130057999</v>
       </c>
       <c r="B33" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>130057989</v>
       </c>
       <c r="B34" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>130058011</v>
       </c>
       <c r="B35" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>130058012</v>
       </c>
       <c r="B36" t="n">
-        <v>80235</v>
+        <v>80320</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4189,10 +4189,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130057983</v>
+        <v>130057997</v>
       </c>
       <c r="B37" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575080</v>
+        <v>575343</v>
       </c>
       <c r="R37" t="n">
-        <v>6970402</v>
+        <v>6970427</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4291,10 +4291,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130057978</v>
+        <v>130057983</v>
       </c>
       <c r="B38" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4326,10 +4326,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575331</v>
+        <v>575080</v>
       </c>
       <c r="R38" t="n">
-        <v>6970309</v>
+        <v>6970402</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4393,10 +4393,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130057997</v>
+        <v>130057978</v>
       </c>
       <c r="B39" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>575343</v>
+        <v>575331</v>
       </c>
       <c r="R39" t="n">
-        <v>6970427</v>
+        <v>6970309</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4498,7 +4498,7 @@
         <v>130057996</v>
       </c>
       <c r="B40" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 59107-2025 artfynd.xlsx
+++ b/artfynd/A 59107-2025 artfynd.xlsx
@@ -2602,10 +2602,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130057985</v>
+        <v>130058004</v>
       </c>
       <c r="B21" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2613,21 +2613,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574905</v>
+        <v>575255</v>
       </c>
       <c r="R21" t="n">
-        <v>6970496</v>
+        <v>6970243</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2673,11 +2673,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2704,7 +2699,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130057975</v>
+        <v>130057985</v>
       </c>
       <c r="B22" t="n">
         <v>57826</v>
@@ -2739,10 +2734,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575392</v>
+        <v>574905</v>
       </c>
       <c r="R22" t="n">
-        <v>6970254</v>
+        <v>6970496</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2806,10 +2801,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130058004</v>
+        <v>130057975</v>
       </c>
       <c r="B23" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2817,21 +2812,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2841,10 +2836,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575255</v>
+        <v>575392</v>
       </c>
       <c r="R23" t="n">
-        <v>6970243</v>
+        <v>6970254</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2877,6 +2872,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 59107-2025 artfynd.xlsx
+++ b/artfynd/A 59107-2025 artfynd.xlsx
@@ -3199,10 +3199,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130057974</v>
+        <v>130058001</v>
       </c>
       <c r="B27" t="n">
-        <v>57826</v>
+        <v>80286</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3210,21 +3210,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575394</v>
+        <v>575248</v>
       </c>
       <c r="R27" t="n">
-        <v>6970263</v>
+        <v>6970510</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3270,11 +3270,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3301,10 +3296,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130058001</v>
+        <v>130057974</v>
       </c>
       <c r="B28" t="n">
-        <v>80286</v>
+        <v>57826</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3312,21 +3307,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3336,10 +3331,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575248</v>
+        <v>575394</v>
       </c>
       <c r="R28" t="n">
-        <v>6970510</v>
+        <v>6970263</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3372,6 +3367,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 59107-2025 artfynd.xlsx
+++ b/artfynd/A 59107-2025 artfynd.xlsx
@@ -2194,7 +2194,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130057998</v>
+        <v>130057982</v>
       </c>
       <c r="B17" t="n">
         <v>57826</v>
@@ -2229,10 +2229,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575378</v>
+        <v>575171</v>
       </c>
       <c r="R17" t="n">
-        <v>6970293</v>
+        <v>6970392</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,7 +2296,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130057982</v>
+        <v>130057986</v>
       </c>
       <c r="B18" t="n">
         <v>57826</v>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575171</v>
+        <v>574906</v>
       </c>
       <c r="R18" t="n">
-        <v>6970392</v>
+        <v>6970504</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2398,7 +2398,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130057986</v>
+        <v>130057998</v>
       </c>
       <c r="B19" t="n">
         <v>57826</v>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574906</v>
+        <v>575378</v>
       </c>
       <c r="R19" t="n">
-        <v>6970504</v>
+        <v>6970293</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3791,10 +3791,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130057999</v>
+        <v>130058011</v>
       </c>
       <c r="B33" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3802,21 +3802,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>575387</v>
+        <v>575417</v>
       </c>
       <c r="R33" t="n">
-        <v>6970271</v>
+        <v>6970259</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3862,11 +3862,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3893,7 +3888,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130057989</v>
+        <v>130057999</v>
       </c>
       <c r="B34" t="n">
         <v>57826</v>
@@ -3928,10 +3923,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575153</v>
+        <v>575387</v>
       </c>
       <c r="R34" t="n">
-        <v>6970582</v>
+        <v>6970271</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3995,10 +3990,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130058011</v>
+        <v>130057989</v>
       </c>
       <c r="B35" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4006,21 +4001,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4030,10 +4025,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575417</v>
+        <v>575153</v>
       </c>
       <c r="R35" t="n">
-        <v>6970259</v>
+        <v>6970582</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4066,6 +4061,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4189,7 +4189,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130057997</v>
+        <v>130057983</v>
       </c>
       <c r="B37" t="n">
         <v>57826</v>
@@ -4224,10 +4224,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575343</v>
+        <v>575080</v>
       </c>
       <c r="R37" t="n">
-        <v>6970427</v>
+        <v>6970402</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4291,7 +4291,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130057983</v>
+        <v>130057997</v>
       </c>
       <c r="B38" t="n">
         <v>57826</v>
@@ -4326,10 +4326,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575080</v>
+        <v>575343</v>
       </c>
       <c r="R38" t="n">
-        <v>6970402</v>
+        <v>6970427</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>

--- a/artfynd/A 59107-2025 artfynd.xlsx
+++ b/artfynd/A 59107-2025 artfynd.xlsx
@@ -3398,32 +3398,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130058005</v>
+        <v>130058008</v>
       </c>
       <c r="B29" t="n">
-        <v>80285</v>
+        <v>80321</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575268</v>
+        <v>575396</v>
       </c>
       <c r="R29" t="n">
-        <v>6970343</v>
+        <v>6970178</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3495,32 +3495,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130058008</v>
+        <v>130058005</v>
       </c>
       <c r="B30" t="n">
-        <v>80321</v>
+        <v>80285</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3530,10 +3530,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575396</v>
+        <v>575268</v>
       </c>
       <c r="R30" t="n">
-        <v>6970178</v>
+        <v>6970343</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4092,32 +4092,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130058012</v>
+        <v>130057983</v>
       </c>
       <c r="B36" t="n">
-        <v>80320</v>
+        <v>57826</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4127,10 +4127,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575222</v>
+        <v>575080</v>
       </c>
       <c r="R36" t="n">
-        <v>6970329</v>
+        <v>6970402</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4163,6 +4163,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4189,7 +4194,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130057983</v>
+        <v>130057997</v>
       </c>
       <c r="B37" t="n">
         <v>57826</v>
@@ -4224,10 +4229,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575080</v>
+        <v>575343</v>
       </c>
       <c r="R37" t="n">
-        <v>6970402</v>
+        <v>6970427</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4291,7 +4296,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130057997</v>
+        <v>130057978</v>
       </c>
       <c r="B38" t="n">
         <v>57826</v>
@@ -4326,10 +4331,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575343</v>
+        <v>575331</v>
       </c>
       <c r="R38" t="n">
-        <v>6970427</v>
+        <v>6970309</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4393,32 +4398,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130057978</v>
+        <v>130058012</v>
       </c>
       <c r="B39" t="n">
-        <v>57826</v>
+        <v>80320</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4428,10 +4433,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>575331</v>
+        <v>575222</v>
       </c>
       <c r="R39" t="n">
-        <v>6970309</v>
+        <v>6970329</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4464,11 +4469,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 59107-2025 artfynd.xlsx
+++ b/artfynd/A 59107-2025 artfynd.xlsx
@@ -990,32 +990,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130058013</v>
+        <v>130057976</v>
       </c>
       <c r="B5" t="n">
-        <v>80320</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575046</v>
+        <v>575355</v>
       </c>
       <c r="R5" t="n">
-        <v>6970437</v>
+        <v>6970253</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,6 +1061,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130057976</v>
+        <v>130057987</v>
       </c>
       <c r="B6" t="n">
         <v>57826</v>
@@ -1122,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575355</v>
+        <v>575159</v>
       </c>
       <c r="R6" t="n">
-        <v>6970253</v>
+        <v>6970484</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,32 +1194,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130057987</v>
+        <v>130058013</v>
       </c>
       <c r="B7" t="n">
-        <v>57826</v>
+        <v>80320</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1224,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575159</v>
+        <v>575046</v>
       </c>
       <c r="R7" t="n">
-        <v>6970484</v>
+        <v>6970437</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,11 +1265,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2097,32 +2097,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130058000</v>
+        <v>130057982</v>
       </c>
       <c r="B16" t="n">
-        <v>80314</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575245</v>
+        <v>575171</v>
       </c>
       <c r="R16" t="n">
-        <v>6970511</v>
+        <v>6970392</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,6 +2168,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2194,7 +2199,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130057982</v>
+        <v>130057986</v>
       </c>
       <c r="B17" t="n">
         <v>57826</v>
@@ -2229,10 +2234,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575171</v>
+        <v>574906</v>
       </c>
       <c r="R17" t="n">
-        <v>6970392</v>
+        <v>6970504</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2296,7 +2301,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130057986</v>
+        <v>130057998</v>
       </c>
       <c r="B18" t="n">
         <v>57826</v>
@@ -2331,10 +2336,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574906</v>
+        <v>575378</v>
       </c>
       <c r="R18" t="n">
-        <v>6970504</v>
+        <v>6970293</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2398,7 +2403,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130057998</v>
+        <v>130057984</v>
       </c>
       <c r="B19" t="n">
         <v>57826</v>
@@ -2433,10 +2438,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575378</v>
+        <v>574929</v>
       </c>
       <c r="R19" t="n">
-        <v>6970293</v>
+        <v>6970479</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2500,32 +2505,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130057984</v>
+        <v>130058000</v>
       </c>
       <c r="B20" t="n">
-        <v>57826</v>
+        <v>80314</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2535,10 +2540,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574929</v>
+        <v>575245</v>
       </c>
       <c r="R20" t="n">
-        <v>6970479</v>
+        <v>6970511</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2571,11 +2576,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3398,32 +3398,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130058008</v>
+        <v>130058005</v>
       </c>
       <c r="B29" t="n">
-        <v>80321</v>
+        <v>80285</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575396</v>
+        <v>575268</v>
       </c>
       <c r="R29" t="n">
-        <v>6970178</v>
+        <v>6970343</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3495,32 +3495,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130058005</v>
+        <v>130058008</v>
       </c>
       <c r="B30" t="n">
-        <v>80285</v>
+        <v>80321</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3530,10 +3530,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575268</v>
+        <v>575396</v>
       </c>
       <c r="R30" t="n">
-        <v>6970343</v>
+        <v>6970178</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4092,32 +4092,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130057983</v>
+        <v>130058012</v>
       </c>
       <c r="B36" t="n">
-        <v>57826</v>
+        <v>80320</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4127,10 +4127,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575080</v>
+        <v>575222</v>
       </c>
       <c r="R36" t="n">
-        <v>6970402</v>
+        <v>6970329</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4163,11 +4163,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4194,7 +4189,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130057997</v>
+        <v>130057983</v>
       </c>
       <c r="B37" t="n">
         <v>57826</v>
@@ -4229,10 +4224,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575343</v>
+        <v>575080</v>
       </c>
       <c r="R37" t="n">
-        <v>6970427</v>
+        <v>6970402</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4296,7 +4291,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130057978</v>
+        <v>130057997</v>
       </c>
       <c r="B38" t="n">
         <v>57826</v>
@@ -4331,10 +4326,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575331</v>
+        <v>575343</v>
       </c>
       <c r="R38" t="n">
-        <v>6970309</v>
+        <v>6970427</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4398,32 +4393,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130058012</v>
+        <v>130057978</v>
       </c>
       <c r="B39" t="n">
-        <v>80320</v>
+        <v>57826</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4433,10 +4428,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>575222</v>
+        <v>575331</v>
       </c>
       <c r="R39" t="n">
-        <v>6970329</v>
+        <v>6970309</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4469,6 +4464,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 59107-2025 artfynd.xlsx
+++ b/artfynd/A 59107-2025 artfynd.xlsx
@@ -990,32 +990,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130058013</v>
+        <v>130057976</v>
       </c>
       <c r="B5" t="n">
-        <v>80320</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575046</v>
+        <v>575355</v>
       </c>
       <c r="R5" t="n">
-        <v>6970437</v>
+        <v>6970253</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,6 +1061,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130057976</v>
+        <v>130057987</v>
       </c>
       <c r="B6" t="n">
         <v>57826</v>
@@ -1122,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575355</v>
+        <v>575159</v>
       </c>
       <c r="R6" t="n">
-        <v>6970253</v>
+        <v>6970484</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,32 +1194,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130057987</v>
+        <v>130058013</v>
       </c>
       <c r="B7" t="n">
-        <v>57826</v>
+        <v>80320</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1224,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575159</v>
+        <v>575046</v>
       </c>
       <c r="R7" t="n">
-        <v>6970484</v>
+        <v>6970437</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,11 +1265,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2602,10 +2602,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130058004</v>
+        <v>130057985</v>
       </c>
       <c r="B21" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2613,21 +2613,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575255</v>
+        <v>574905</v>
       </c>
       <c r="R21" t="n">
-        <v>6970243</v>
+        <v>6970496</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2673,6 +2673,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2699,7 +2704,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130057985</v>
+        <v>130057975</v>
       </c>
       <c r="B22" t="n">
         <v>57826</v>
@@ -2734,10 +2739,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574905</v>
+        <v>575392</v>
       </c>
       <c r="R22" t="n">
-        <v>6970496</v>
+        <v>6970254</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2801,10 +2806,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130057975</v>
+        <v>130058004</v>
       </c>
       <c r="B23" t="n">
-        <v>57826</v>
+        <v>80285</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,21 +2817,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2836,10 +2841,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575392</v>
+        <v>575255</v>
       </c>
       <c r="R23" t="n">
-        <v>6970254</v>
+        <v>6970243</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2872,11 +2877,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3199,10 +3199,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130057974</v>
+        <v>130058001</v>
       </c>
       <c r="B27" t="n">
-        <v>57826</v>
+        <v>80286</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3210,21 +3210,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575394</v>
+        <v>575248</v>
       </c>
       <c r="R27" t="n">
-        <v>6970263</v>
+        <v>6970510</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3270,11 +3270,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3301,10 +3296,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130058001</v>
+        <v>130057974</v>
       </c>
       <c r="B28" t="n">
-        <v>80286</v>
+        <v>57826</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3312,21 +3307,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3336,10 +3331,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575248</v>
+        <v>575394</v>
       </c>
       <c r="R28" t="n">
-        <v>6970510</v>
+        <v>6970263</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3372,6 +3367,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4092,7 +4092,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130057997</v>
+        <v>130057983</v>
       </c>
       <c r="B36" t="n">
         <v>57826</v>
@@ -4127,10 +4127,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575343</v>
+        <v>575080</v>
       </c>
       <c r="R36" t="n">
-        <v>6970427</v>
+        <v>6970402</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4194,32 +4194,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130058012</v>
+        <v>130057978</v>
       </c>
       <c r="B37" t="n">
-        <v>80320</v>
+        <v>57826</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4229,10 +4229,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>575222</v>
+        <v>575331</v>
       </c>
       <c r="R37" t="n">
-        <v>6970329</v>
+        <v>6970309</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4265,6 +4265,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4291,7 +4296,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130057983</v>
+        <v>130057997</v>
       </c>
       <c r="B38" t="n">
         <v>57826</v>
@@ -4326,10 +4331,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575080</v>
+        <v>575343</v>
       </c>
       <c r="R38" t="n">
-        <v>6970402</v>
+        <v>6970427</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4393,32 +4398,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130057978</v>
+        <v>130058012</v>
       </c>
       <c r="B39" t="n">
-        <v>57826</v>
+        <v>80320</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4428,10 +4433,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>575331</v>
+        <v>575222</v>
       </c>
       <c r="R39" t="n">
-        <v>6970309</v>
+        <v>6970329</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4464,11 +4469,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
